--- a/Q3_Q4_LYV_venue_pivots.xlsx
+++ b/Q3_Q4_LYV_venue_pivots.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -476,7 +476,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Q3 2024 - Live Nation promoted</t>
+          <t>Q1 2024 - Live Nation promoted</t>
         </is>
       </c>
     </row>
@@ -524,22 +524,22 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>764</v>
+        <v>533</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>831</v>
+        <v>625</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>8801831</v>
+        <v>6302761</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>1020346599.55</v>
+        <v>885217552.1799999</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>115.92</v>
+        <v>140.45</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>1227853.91</v>
+        <v>1416348.08</v>
       </c>
     </row>
     <row r="4">
@@ -549,22 +549,22 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>708</v>
+        <v>18</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>733</v>
+        <v>19</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>8134830</v>
+        <v>130573</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>521398460.91</v>
+        <v>10928098.05</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>64.09</v>
+        <v>83.69</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>711321.23</v>
+        <v>575163.0600000001</v>
       </c>
     </row>
     <row r="5">
@@ -574,22 +574,22 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>173</v>
+        <v>45</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>205</v>
+        <v>77</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>8440593</v>
+        <v>3459632</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>1038171101.51</v>
+        <v>404396755.15</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>123</v>
+        <v>116.89</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>5064249.28</v>
+        <v>5251905.91</v>
       </c>
     </row>
     <row r="6">
@@ -599,22 +599,22 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>627</v>
+        <v>560</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>635</v>
+        <v>574</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>657503</v>
+        <v>438453</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>33634694.65</v>
+        <v>17854773.91</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>51.16</v>
+        <v>40.72</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>52968.02</v>
+        <v>31105.88</v>
       </c>
     </row>
     <row r="7">
@@ -624,22 +624,22 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>700</v>
+        <v>582</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>824</v>
+        <v>806</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1943077</v>
+        <v>1765707</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>156322089.93</v>
+        <v>125598660.55</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>80.45</v>
+        <v>71.13</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>189711.27</v>
+        <v>155829.6</v>
       </c>
     </row>
     <row r="8">
@@ -649,22 +649,22 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>134</v>
+        <v>51</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>153</v>
+        <v>61</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>857819</v>
+        <v>354193</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>63120340.25</v>
+        <v>20897937.73</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>73.58</v>
+        <v>59</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>412551.24</v>
+        <v>342589.14</v>
       </c>
     </row>
     <row r="9">
@@ -674,28 +674,28 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>3106</v>
+        <v>1789</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>3381</v>
+        <v>2162</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>28835653</v>
+        <v>12451319</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>2832993286.8</v>
+        <v>1464893777.57</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>98.25</v>
+        <v>117.65</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>837915.79</v>
+        <v>677564.1899999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>Latest reported show date in this cell: 09/30/2024</t>
+          <t>Latest reported show date in this cell: 03/31/2024</t>
         </is>
       </c>
     </row>
@@ -703,7 +703,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Q3 2025 - Live Nation promoted</t>
+          <t>Q2 2024 - Live Nation promoted</t>
         </is>
       </c>
     </row>
@@ -751,22 +751,22 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>645</v>
+        <v>796</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>726</v>
+        <v>897</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>8008049</v>
+        <v>9297027</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>959468671.88</v>
+        <v>1141372999.72</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>119.81</v>
+        <v>122.77</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>1321582.19</v>
+        <v>1272433.67</v>
       </c>
     </row>
     <row r="15">
@@ -776,22 +776,22 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>566</v>
+        <v>320</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>583</v>
+        <v>328</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>6123795</v>
+        <v>3777590</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>392129657.64</v>
+        <v>253854462.29</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>64.03</v>
+        <v>67.2</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>672606.62</v>
+        <v>773946.53</v>
       </c>
     </row>
     <row r="16">
@@ -801,22 +801,22 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>223</v>
+        <v>90</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>285</v>
+        <v>108</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>10529321</v>
+        <v>2928987</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1463972588.76</v>
+        <v>314604148.68</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>139.04</v>
+        <v>107.41</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>5136745.93</v>
+        <v>2913001.38</v>
       </c>
     </row>
     <row r="17">
@@ -826,22 +826,22 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>512</v>
+        <v>734</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>519</v>
+        <v>749</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>476609</v>
+        <v>619721</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>24300468.53</v>
+        <v>28129039.6</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>50.99</v>
+        <v>45.39</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>46821.71</v>
+        <v>37555.46</v>
       </c>
     </row>
     <row r="18">
@@ -851,22 +851,22 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>491</v>
+        <v>809</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>623</v>
+        <v>965</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1459443</v>
+        <v>2369836</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>115519649.75</v>
+        <v>180892765.66</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>79.15000000000001</v>
+        <v>76.33</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>185424.8</v>
+        <v>187453.64</v>
       </c>
     </row>
     <row r="19">
@@ -876,22 +876,22 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>80</v>
+        <v>121</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>86</v>
+        <v>126</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>598462</v>
+        <v>457436</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>67496108.45</v>
+        <v>36465906.47</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>112.78</v>
+        <v>79.72</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>784838.47</v>
+        <v>289411.96</v>
       </c>
     </row>
     <row r="20">
@@ -901,28 +901,28 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>2517</v>
+        <v>2870</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>2822</v>
+        <v>3173</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>27195679</v>
+        <v>19450597</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>3022887145.01</v>
+        <v>1955319322.42</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>111.15</v>
+        <v>100.53</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>1071186.09</v>
+        <v>616236.79</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>Latest reported show date in this cell: 09/30/2025</t>
+          <t>Latest reported show date in this cell: 06/30/2024</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Q3 2026 - Live Nation promoted</t>
+          <t>Q3 2024 - Live Nation promoted</t>
         </is>
       </c>
     </row>
@@ -978,22 +978,22 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>314</v>
+        <v>764</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>381</v>
+        <v>831</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>4512301</v>
+        <v>8801831</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>580123925.65</v>
+        <v>1020346599.55</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>128.56</v>
+        <v>115.92</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>1522634.98</v>
+        <v>1227853.91</v>
       </c>
     </row>
     <row r="26">
@@ -1003,22 +1003,22 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>255</v>
+        <v>708</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>265</v>
+        <v>733</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>3338705</v>
+        <v>8134830</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>212107689.02</v>
+        <v>521398460.91</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>63.53</v>
+        <v>64.09</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>800406.37</v>
+        <v>711321.23</v>
       </c>
     </row>
     <row r="27">
@@ -1028,22 +1028,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>9573013</v>
+        <v>8440593</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1510081963.63</v>
+        <v>1038171101.51</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>157.74</v>
+        <v>123</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>7475653.29</v>
+        <v>5064249.28</v>
       </c>
     </row>
     <row r="28">
@@ -1053,22 +1053,22 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>201</v>
+        <v>627</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>206</v>
+        <v>635</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>271923</v>
+        <v>657503</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>16236818.33</v>
+        <v>33634694.65</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>59.71</v>
+        <v>51.16</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>78819.50999999999</v>
+        <v>52968.02</v>
       </c>
     </row>
     <row r="29">
@@ -1078,22 +1078,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>211</v>
+        <v>700</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>379</v>
+        <v>824</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>762333</v>
+        <v>1943077</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>60574122.36</v>
+        <v>156322089.93</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>79.45999999999999</v>
+        <v>80.45</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>159826.18</v>
+        <v>189711.27</v>
       </c>
     </row>
     <row r="30">
@@ -1103,22 +1103,22 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>15</v>
+        <v>134</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>16</v>
+        <v>153</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>305539</v>
+        <v>857819</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>38199002.05</v>
+        <v>63120340.25</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>125.02</v>
+        <v>73.58</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>2387437.63</v>
+        <v>412551.24</v>
       </c>
     </row>
     <row r="31">
@@ -1128,28 +1128,28 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>1162</v>
+        <v>3106</v>
       </c>
       <c r="C31" s="6" t="n">
-        <v>1449</v>
+        <v>3381</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>18763814</v>
+        <v>28835653</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>2417323521.04</v>
+        <v>2832993286.8</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>128.83</v>
+        <v>98.25</v>
       </c>
       <c r="G31" s="8" t="n">
-        <v>1668270.2</v>
+        <v>837915.79</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>Latest reported show date in this cell: 09/27/2026</t>
+          <t>Latest reported show date in this cell: 09/30/2024</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>Q4 2025 - Live Nation promoted</t>
+          <t>Q1 2025 - Live Nation promoted</t>
         </is>
       </c>
     </row>
@@ -1432,22 +1432,22 @@
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>772</v>
+        <v>406</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>897</v>
+        <v>446</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>8685301</v>
+        <v>4752723</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>905548614.2</v>
+        <v>538814765.8200001</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>104.26</v>
+        <v>113.37</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>1009530.23</v>
+        <v>1208104.86</v>
       </c>
     </row>
     <row r="48">
@@ -1457,22 +1457,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>99</v>
+        <v>16</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>106</v>
+        <v>16</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>940107</v>
+        <v>70170</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>70825655.51000001</v>
+        <v>4870489.91</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>75.34</v>
+        <v>69.41</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>668166.5600000001</v>
+        <v>304405.62</v>
       </c>
     </row>
     <row r="49">
@@ -1482,22 +1482,22 @@
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>111</v>
+        <v>55</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>130</v>
+        <v>78</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>4995654</v>
+        <v>3123049</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>579357268.86</v>
+        <v>326785015.49</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>115.97</v>
+        <v>104.64</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>4456594.38</v>
+        <v>4189551.48</v>
       </c>
     </row>
     <row r="50">
@@ -1507,22 +1507,22 @@
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>824</v>
+        <v>601</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>837</v>
+        <v>619</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>629647</v>
+        <v>473420</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>27987293.1</v>
+        <v>20038961.68</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>44.45</v>
+        <v>42.33</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>33437.63</v>
+        <v>32373.12</v>
       </c>
     </row>
     <row r="51">
@@ -1532,22 +1532,22 @@
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>845</v>
+        <v>627</v>
       </c>
       <c r="C51" s="3" t="n">
-        <v>1150</v>
+        <v>697</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>2400370</v>
+        <v>1558330</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>183400099.65</v>
+        <v>119478048.05</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>76.40000000000001</v>
+        <v>76.67</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>159478.35</v>
+        <v>171417.57</v>
       </c>
     </row>
     <row r="52">
@@ -1557,22 +1557,22 @@
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="C52" s="3" t="n">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>353336</v>
+        <v>204473</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>28775898.24</v>
+        <v>18024875.82</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>81.44</v>
+        <v>88.15000000000001</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>326998.84</v>
+        <v>240331.68</v>
       </c>
     </row>
     <row r="53">
@@ -1582,28 +1582,1390 @@
         </is>
       </c>
       <c r="B53" s="6" t="n">
-        <v>2737</v>
+        <v>1759</v>
       </c>
       <c r="C53" s="6" t="n">
-        <v>3208</v>
+        <v>1931</v>
       </c>
       <c r="D53" s="6" t="n">
-        <v>18004415</v>
+        <v>10182165</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>1795894829.56</v>
+        <v>1028012156.77</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>99.75</v>
+        <v>100.96</v>
       </c>
       <c r="G53" s="8" t="n">
-        <v>559817.59</v>
+        <v>532372.9399999999</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="9" t="inlineStr">
         <is>
+          <t>Latest reported show date in this cell: 03/31/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="55"/>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>Q2 2025 - Live Nation promoted</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Venue Type</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Num Shows</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Tickets Sold</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Total Gross</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Avg Ticket Price</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>Avg Gross per Show</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>Arena</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>591</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>650</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>6180346</v>
+      </c>
+      <c r="E58" s="4" t="n">
+        <v>653364259.74</v>
+      </c>
+      <c r="F58" s="5" t="n">
+        <v>105.72</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>1005175.78</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>Amphitheatre</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>258</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>265</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>2646422</v>
+      </c>
+      <c r="E59" s="4" t="n">
+        <v>170544780.04</v>
+      </c>
+      <c r="F59" s="5" t="n">
+        <v>64.44</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>643565.21</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>Stadium</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>276</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>356</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>12310269</v>
+      </c>
+      <c r="E60" s="4" t="n">
+        <v>1818858263.01</v>
+      </c>
+      <c r="F60" s="5" t="n">
+        <v>147.75</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>5109152.42</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>Club</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>756</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>771</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>666350</v>
+      </c>
+      <c r="E61" s="4" t="n">
+        <v>30345218.1</v>
+      </c>
+      <c r="F61" s="5" t="n">
+        <v>45.54</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>39358.26</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>Theater</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>676</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>810</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>1885830</v>
+      </c>
+      <c r="E62" s="4" t="n">
+        <v>143858849.19</v>
+      </c>
+      <c r="F62" s="5" t="n">
+        <v>76.28</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>177603.52</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>69</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>459642</v>
+      </c>
+      <c r="E63" s="4" t="n">
+        <v>37029275.76</v>
+      </c>
+      <c r="F63" s="5" t="n">
+        <v>80.56</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>507250.35</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="n">
+        <v>2626</v>
+      </c>
+      <c r="C64" s="6" t="n">
+        <v>2925</v>
+      </c>
+      <c r="D64" s="6" t="n">
+        <v>24148859</v>
+      </c>
+      <c r="E64" s="7" t="n">
+        <v>2854000645.84</v>
+      </c>
+      <c r="F64" s="8" t="n">
+        <v>118.18</v>
+      </c>
+      <c r="G64" s="8" t="n">
+        <v>975726.72</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="9" t="inlineStr">
+        <is>
+          <t>Latest reported show date in this cell: 06/30/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="66"/>
+    <row r="67">
+      <c r="A67" s="1" t="inlineStr">
+        <is>
+          <t>Q3 2025 - Live Nation promoted</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Venue Type</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Num Shows</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Tickets Sold</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Total Gross</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>Avg Ticket Price</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>Avg Gross per Show</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>Arena</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v>645</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>726</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>8008049</v>
+      </c>
+      <c r="E69" s="4" t="n">
+        <v>959468671.88</v>
+      </c>
+      <c r="F69" s="5" t="n">
+        <v>119.81</v>
+      </c>
+      <c r="G69" s="5" t="n">
+        <v>1321582.19</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>Amphitheatre</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v>566</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>583</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>6123795</v>
+      </c>
+      <c r="E70" s="4" t="n">
+        <v>392129657.64</v>
+      </c>
+      <c r="F70" s="5" t="n">
+        <v>64.03</v>
+      </c>
+      <c r="G70" s="5" t="n">
+        <v>672606.62</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>Stadium</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v>223</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>285</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>10529321</v>
+      </c>
+      <c r="E71" s="4" t="n">
+        <v>1463972588.76</v>
+      </c>
+      <c r="F71" s="5" t="n">
+        <v>139.04</v>
+      </c>
+      <c r="G71" s="5" t="n">
+        <v>5136745.93</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>Club</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v>512</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>519</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>476609</v>
+      </c>
+      <c r="E72" s="4" t="n">
+        <v>24300468.53</v>
+      </c>
+      <c r="F72" s="5" t="n">
+        <v>50.99</v>
+      </c>
+      <c r="G72" s="5" t="n">
+        <v>46821.71</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>Theater</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="n">
+        <v>491</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>623</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>1459443</v>
+      </c>
+      <c r="E73" s="4" t="n">
+        <v>115519649.75</v>
+      </c>
+      <c r="F73" s="5" t="n">
+        <v>79.15000000000001</v>
+      </c>
+      <c r="G73" s="5" t="n">
+        <v>185424.8</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>86</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>598462</v>
+      </c>
+      <c r="E74" s="4" t="n">
+        <v>67496108.45</v>
+      </c>
+      <c r="F74" s="5" t="n">
+        <v>112.78</v>
+      </c>
+      <c r="G74" s="5" t="n">
+        <v>784838.47</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="n">
+        <v>2517</v>
+      </c>
+      <c r="C75" s="6" t="n">
+        <v>2822</v>
+      </c>
+      <c r="D75" s="6" t="n">
+        <v>27195679</v>
+      </c>
+      <c r="E75" s="7" t="n">
+        <v>3022887145.01</v>
+      </c>
+      <c r="F75" s="8" t="n">
+        <v>111.15</v>
+      </c>
+      <c r="G75" s="8" t="n">
+        <v>1071186.09</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="9" t="inlineStr">
+        <is>
+          <t>Latest reported show date in this cell: 09/30/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="77"/>
+    <row r="78">
+      <c r="A78" s="1" t="inlineStr">
+        <is>
+          <t>Q4 2025 - Live Nation promoted</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Venue Type</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Num Shows</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Tickets Sold</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>Total Gross</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>Avg Ticket Price</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>Avg Gross per Show</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>Arena</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="n">
+        <v>772</v>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>897</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>8685301</v>
+      </c>
+      <c r="E80" s="4" t="n">
+        <v>905548614.2</v>
+      </c>
+      <c r="F80" s="5" t="n">
+        <v>104.26</v>
+      </c>
+      <c r="G80" s="5" t="n">
+        <v>1009530.23</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>Amphitheatre</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="n">
+        <v>99</v>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>106</v>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>940107</v>
+      </c>
+      <c r="E81" s="4" t="n">
+        <v>70825655.51000001</v>
+      </c>
+      <c r="F81" s="5" t="n">
+        <v>75.34</v>
+      </c>
+      <c r="G81" s="5" t="n">
+        <v>668166.5600000001</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>Stadium</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="n">
+        <v>111</v>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>4995654</v>
+      </c>
+      <c r="E82" s="4" t="n">
+        <v>579357268.86</v>
+      </c>
+      <c r="F82" s="5" t="n">
+        <v>115.97</v>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>4456594.38</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>Club</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="n">
+        <v>824</v>
+      </c>
+      <c r="C83" s="3" t="n">
+        <v>837</v>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>629647</v>
+      </c>
+      <c r="E83" s="4" t="n">
+        <v>27987293.1</v>
+      </c>
+      <c r="F83" s="5" t="n">
+        <v>44.45</v>
+      </c>
+      <c r="G83" s="5" t="n">
+        <v>33437.63</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>Theater</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="n">
+        <v>845</v>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>1150</v>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>2400370</v>
+      </c>
+      <c r="E84" s="4" t="n">
+        <v>183400099.65</v>
+      </c>
+      <c r="F84" s="5" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="G84" s="5" t="n">
+        <v>159478.35</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="n">
+        <v>86</v>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>353336</v>
+      </c>
+      <c r="E85" s="4" t="n">
+        <v>28775898.24</v>
+      </c>
+      <c r="F85" s="5" t="n">
+        <v>81.44</v>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>326998.84</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="n">
+        <v>2737</v>
+      </c>
+      <c r="C86" s="6" t="n">
+        <v>3208</v>
+      </c>
+      <c r="D86" s="6" t="n">
+        <v>18004415</v>
+      </c>
+      <c r="E86" s="7" t="n">
+        <v>1795894829.56</v>
+      </c>
+      <c r="F86" s="8" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="G86" s="8" t="n">
+        <v>559817.59</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="9" t="inlineStr">
+        <is>
           <t>Latest reported show date in this cell: 12/31/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="88"/>
+    <row r="89">
+      <c r="A89" s="1" t="inlineStr">
+        <is>
+          <t>Q1 2026 - Live Nation promoted</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Venue Type</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Num Shows</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Tickets Sold</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>Total Gross</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>Avg Ticket Price</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>Avg Gross per Show</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>Arena</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="n">
+        <v>428</v>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>470</v>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>4785010</v>
+      </c>
+      <c r="E91" s="4" t="n">
+        <v>580938201.4400001</v>
+      </c>
+      <c r="F91" s="5" t="n">
+        <v>121.41</v>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>1236038.73</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>Amphitheatre</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C92" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="D92" s="3" t="n">
+        <v>107644</v>
+      </c>
+      <c r="E92" s="4" t="n">
+        <v>8681755.67</v>
+      </c>
+      <c r="F92" s="5" t="n">
+        <v>80.65000000000001</v>
+      </c>
+      <c r="G92" s="5" t="n">
+        <v>482319.76</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>Stadium</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="C93" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="D93" s="3" t="n">
+        <v>3118917</v>
+      </c>
+      <c r="E93" s="4" t="n">
+        <v>426460735.85</v>
+      </c>
+      <c r="F93" s="5" t="n">
+        <v>136.73</v>
+      </c>
+      <c r="G93" s="5" t="n">
+        <v>7228148.07</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>Club</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="n">
+        <v>548</v>
+      </c>
+      <c r="C94" s="3" t="n">
+        <v>563</v>
+      </c>
+      <c r="D94" s="3" t="n">
+        <v>435197</v>
+      </c>
+      <c r="E94" s="4" t="n">
+        <v>18373295.76</v>
+      </c>
+      <c r="F94" s="5" t="n">
+        <v>42.22</v>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>32634.63</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>Theater</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="n">
+        <v>601</v>
+      </c>
+      <c r="C95" s="3" t="n">
+        <v>890</v>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>1582348</v>
+      </c>
+      <c r="E95" s="4" t="n">
+        <v>131486826.62</v>
+      </c>
+      <c r="F95" s="5" t="n">
+        <v>83.09999999999999</v>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>147738.01</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="C96" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>162331</v>
+      </c>
+      <c r="E96" s="4" t="n">
+        <v>15752274.9</v>
+      </c>
+      <c r="F96" s="5" t="n">
+        <v>97.04000000000001</v>
+      </c>
+      <c r="G96" s="5" t="n">
+        <v>315045.5</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B97" s="6" t="n">
+        <v>1680</v>
+      </c>
+      <c r="C97" s="6" t="n">
+        <v>2050</v>
+      </c>
+      <c r="D97" s="6" t="n">
+        <v>10191447</v>
+      </c>
+      <c r="E97" s="7" t="n">
+        <v>1181693090.24</v>
+      </c>
+      <c r="F97" s="8" t="n">
+        <v>115.95</v>
+      </c>
+      <c r="G97" s="8" t="n">
+        <v>576435.65</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="9" t="inlineStr">
+        <is>
+          <t>Latest reported show date in this cell: 03/31/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="99"/>
+    <row r="100">
+      <c r="A100" s="1" t="inlineStr">
+        <is>
+          <t>Q2 2026 - Live Nation promoted</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>Venue Type</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Num Shows</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Tickets Sold</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>Total Gross</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>Avg Ticket Price</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>Avg Gross per Show</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>Arena</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="n">
+        <v>612</v>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>677</v>
+      </c>
+      <c r="D102" s="3" t="n">
+        <v>7281903</v>
+      </c>
+      <c r="E102" s="4" t="n">
+        <v>827929963.45</v>
+      </c>
+      <c r="F102" s="5" t="n">
+        <v>113.7</v>
+      </c>
+      <c r="G102" s="5" t="n">
+        <v>1222939.38</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>Amphitheatre</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="n">
+        <v>202</v>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>209</v>
+      </c>
+      <c r="D103" s="3" t="n">
+        <v>2306795</v>
+      </c>
+      <c r="E103" s="4" t="n">
+        <v>167776894.49</v>
+      </c>
+      <c r="F103" s="5" t="n">
+        <v>72.73</v>
+      </c>
+      <c r="G103" s="5" t="n">
+        <v>802760.26</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>Stadium</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="n">
+        <v>138</v>
+      </c>
+      <c r="C104" s="3" t="n">
+        <v>163</v>
+      </c>
+      <c r="D104" s="3" t="n">
+        <v>5524405</v>
+      </c>
+      <c r="E104" s="4" t="n">
+        <v>763312703.41</v>
+      </c>
+      <c r="F104" s="5" t="n">
+        <v>138.17</v>
+      </c>
+      <c r="G104" s="5" t="n">
+        <v>4682900.02</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>Club</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="n">
+        <v>685</v>
+      </c>
+      <c r="C105" s="3" t="n">
+        <v>1313</v>
+      </c>
+      <c r="D105" s="3" t="n">
+        <v>589102</v>
+      </c>
+      <c r="E105" s="4" t="n">
+        <v>27094459.44</v>
+      </c>
+      <c r="F105" s="5" t="n">
+        <v>45.99</v>
+      </c>
+      <c r="G105" s="5" t="n">
+        <v>20635.54</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>Theater</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="n">
+        <v>695</v>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>956</v>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>1782277</v>
+      </c>
+      <c r="E106" s="4" t="n">
+        <v>137692516.23</v>
+      </c>
+      <c r="F106" s="5" t="n">
+        <v>77.26000000000001</v>
+      </c>
+      <c r="G106" s="5" t="n">
+        <v>144029.83</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="C107" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="D107" s="3" t="n">
+        <v>406789</v>
+      </c>
+      <c r="E107" s="4" t="n">
+        <v>32497605.14</v>
+      </c>
+      <c r="F107" s="5" t="n">
+        <v>79.89</v>
+      </c>
+      <c r="G107" s="5" t="n">
+        <v>396312.26</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B108" s="6" t="n">
+        <v>2407</v>
+      </c>
+      <c r="C108" s="6" t="n">
+        <v>3400</v>
+      </c>
+      <c r="D108" s="6" t="n">
+        <v>17891271</v>
+      </c>
+      <c r="E108" s="7" t="n">
+        <v>1956304142.16</v>
+      </c>
+      <c r="F108" s="8" t="n">
+        <v>109.34</v>
+      </c>
+      <c r="G108" s="8" t="n">
+        <v>575383.5699999999</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="9" t="inlineStr">
+        <is>
+          <t>Latest reported show date in this cell: 06/30/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="110"/>
+    <row r="111">
+      <c r="A111" s="1" t="inlineStr">
+        <is>
+          <t>Q3 2026 - Live Nation promoted</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>Venue Type</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Num Shows</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Tickets Sold</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>Total Gross</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>Avg Ticket Price</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>Avg Gross per Show</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>Arena</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="n">
+        <v>314</v>
+      </c>
+      <c r="C113" s="3" t="n">
+        <v>381</v>
+      </c>
+      <c r="D113" s="3" t="n">
+        <v>4512301</v>
+      </c>
+      <c r="E113" s="4" t="n">
+        <v>580123925.65</v>
+      </c>
+      <c r="F113" s="5" t="n">
+        <v>128.56</v>
+      </c>
+      <c r="G113" s="5" t="n">
+        <v>1522634.98</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="inlineStr">
+        <is>
+          <t>Amphitheatre</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="C114" s="3" t="n">
+        <v>265</v>
+      </c>
+      <c r="D114" s="3" t="n">
+        <v>3338705</v>
+      </c>
+      <c r="E114" s="4" t="n">
+        <v>212107689.02</v>
+      </c>
+      <c r="F114" s="5" t="n">
+        <v>63.53</v>
+      </c>
+      <c r="G114" s="5" t="n">
+        <v>800406.37</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>Stadium</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="n">
+        <v>166</v>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>202</v>
+      </c>
+      <c r="D115" s="3" t="n">
+        <v>9573013</v>
+      </c>
+      <c r="E115" s="4" t="n">
+        <v>1510081963.63</v>
+      </c>
+      <c r="F115" s="5" t="n">
+        <v>157.74</v>
+      </c>
+      <c r="G115" s="5" t="n">
+        <v>7475653.29</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="inlineStr">
+        <is>
+          <t>Club</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="n">
+        <v>201</v>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>206</v>
+      </c>
+      <c r="D116" s="3" t="n">
+        <v>271923</v>
+      </c>
+      <c r="E116" s="4" t="n">
+        <v>16236818.33</v>
+      </c>
+      <c r="F116" s="5" t="n">
+        <v>59.71</v>
+      </c>
+      <c r="G116" s="5" t="n">
+        <v>78819.50999999999</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>Theater</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="n">
+        <v>211</v>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>379</v>
+      </c>
+      <c r="D117" s="3" t="n">
+        <v>762333</v>
+      </c>
+      <c r="E117" s="4" t="n">
+        <v>60574122.36</v>
+      </c>
+      <c r="F117" s="5" t="n">
+        <v>79.45999999999999</v>
+      </c>
+      <c r="G117" s="5" t="n">
+        <v>159826.18</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D118" s="3" t="n">
+        <v>305539</v>
+      </c>
+      <c r="E118" s="4" t="n">
+        <v>38199002.05</v>
+      </c>
+      <c r="F118" s="5" t="n">
+        <v>125.02</v>
+      </c>
+      <c r="G118" s="5" t="n">
+        <v>2387437.63</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="6" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B119" s="6" t="n">
+        <v>1162</v>
+      </c>
+      <c r="C119" s="6" t="n">
+        <v>1449</v>
+      </c>
+      <c r="D119" s="6" t="n">
+        <v>18763814</v>
+      </c>
+      <c r="E119" s="7" t="n">
+        <v>2417323521.04</v>
+      </c>
+      <c r="F119" s="8" t="n">
+        <v>128.83</v>
+      </c>
+      <c r="G119" s="8" t="n">
+        <v>1668270.2</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="9" t="inlineStr">
+        <is>
+          <t>Latest reported show date in this cell: 09/27/2026</t>
         </is>
       </c>
     </row>
@@ -1618,7 +2980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1633,7 +2995,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Q3 2024 - Live Nation owned/operated</t>
+          <t>Q1 2024 - Live Nation owned/operated</t>
         </is>
       </c>
     </row>
@@ -1681,22 +3043,22 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>1507428</v>
+        <v>1388160</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>108583236.38</v>
+        <v>91194066.40000001</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>72.03</v>
+        <v>65.69</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>553996.1</v>
+        <v>521108.95</v>
       </c>
     </row>
     <row r="4">
@@ -1706,22 +3068,22 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>571</v>
+        <v>6</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>597</v>
+        <v>6</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>6954755</v>
+        <v>34344</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>437954790.92</v>
+        <v>1595404.5</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>62.97</v>
+        <v>46.45</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>733592.61</v>
+        <v>265900.75</v>
       </c>
     </row>
     <row r="5">
@@ -1731,22 +3093,22 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>957401</v>
+        <v>460693</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>85160954.81</v>
+        <v>36070342.33</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>88.95</v>
+        <v>78.3</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>3870952.49</v>
+        <v>7214068.47</v>
       </c>
     </row>
     <row r="6">
@@ -1756,22 +3118,22 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>488</v>
+        <v>501</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>256110</v>
+        <v>274804</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>9225596.640000001</v>
+        <v>8760935.92</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>36.02</v>
+        <v>31.88</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>18904.91</v>
+        <v>17486.9</v>
       </c>
     </row>
     <row r="7">
@@ -1781,22 +3143,22 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>530</v>
+        <v>475</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>553</v>
+        <v>583</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>959750</v>
+        <v>898788</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>63617314.07</v>
+        <v>52753830.57</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>66.29000000000001</v>
+        <v>58.69</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>115040.35</v>
+        <v>90486.84</v>
       </c>
     </row>
     <row r="8">
@@ -1806,22 +3168,22 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>82214</v>
+        <v>0</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>11549349.09</v>
+        <v>0</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>140.48</v>
+        <v>0</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>2309869.82</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1831,28 +3193,28 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>1756</v>
+        <v>1114</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>1861</v>
+        <v>1270</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>10717658</v>
+        <v>3056789</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>716091241.91</v>
+        <v>190374579.72</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>66.81</v>
+        <v>62.28</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>384788.42</v>
+        <v>149901.24</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>Latest reported show date in this cell: 09/30/2024</t>
+          <t>Latest reported show date in this cell: 03/31/2024</t>
         </is>
       </c>
     </row>
@@ -1860,7 +3222,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Q3 2025 - Live Nation owned/operated</t>
+          <t>Q2 2024 - Live Nation owned/operated</t>
         </is>
       </c>
     </row>
@@ -1908,22 +3270,22 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>156</v>
+        <v>214</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>220</v>
+        <v>272</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>2044615</v>
+        <v>2303803</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>157627498.13</v>
+        <v>186977791.47</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>77.09</v>
+        <v>81.16</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>716488.63</v>
+        <v>687418.35</v>
       </c>
     </row>
     <row r="15">
@@ -1933,22 +3295,22 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>445</v>
+        <v>237</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>460</v>
+        <v>245</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>5006953</v>
+        <v>3010268</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>314019966.93</v>
+        <v>189117373.17</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>62.72</v>
+        <v>62.82</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>682652.1</v>
+        <v>771907.65</v>
       </c>
     </row>
     <row r="16">
@@ -1958,22 +3320,22 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1568735</v>
+        <v>286340</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>171957973.06</v>
+        <v>22404216.67</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>109.62</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>5210847.67</v>
+        <v>3734036.11</v>
       </c>
     </row>
     <row r="17">
@@ -1983,22 +3345,22 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>365</v>
+        <v>626</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>365</v>
+        <v>637</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>169690</v>
+        <v>330601</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>5736955.65</v>
+        <v>10844626.51</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>33.81</v>
+        <v>32.8</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>15717.69</v>
+        <v>17024.53</v>
       </c>
     </row>
     <row r="18">
@@ -2008,22 +3370,22 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>374</v>
+        <v>576</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>496</v>
+        <v>647</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>786853</v>
+        <v>1095888</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>54531099.07</v>
+        <v>64430933.18</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>69.3</v>
+        <v>58.79</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>109941.73</v>
+        <v>99584.13</v>
       </c>
     </row>
     <row r="19">
@@ -2033,22 +3395,22 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>453045</v>
+        <v>24607</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>91726296.7</v>
+        <v>853662.2</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>202.47</v>
+        <v>34.69</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>11465787.09</v>
+        <v>284554.07</v>
       </c>
     </row>
     <row r="20">
@@ -2058,28 +3420,28 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>1365</v>
+        <v>1659</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>1582</v>
+        <v>1810</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>10029891</v>
+        <v>7051507</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>795599789.54</v>
+        <v>474628603.2</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>79.31999999999999</v>
+        <v>67.31</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>502907.58</v>
+        <v>262225.75</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>Latest reported show date in this cell: 09/30/2025</t>
+          <t>Latest reported show date in this cell: 06/30/2024</t>
         </is>
       </c>
     </row>
@@ -2087,7 +3449,7 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Q3 2026 - Live Nation owned/operated</t>
+          <t>Q3 2024 - Live Nation owned/operated</t>
         </is>
       </c>
     </row>
@@ -2135,22 +3497,22 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>71</v>
+        <v>147</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>102</v>
+        <v>196</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>844983</v>
+        <v>1507428</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>61674894.82</v>
+        <v>108583236.38</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>72.98999999999999</v>
+        <v>72.03</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>604655.83</v>
+        <v>553996.1</v>
       </c>
     </row>
     <row r="26">
@@ -2160,22 +3522,22 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>193</v>
+        <v>571</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>198</v>
+        <v>597</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>2531078</v>
+        <v>6954755</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>153444699.38</v>
+        <v>437954790.92</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>60.62</v>
+        <v>62.97</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>774973.23</v>
+        <v>733592.61</v>
       </c>
     </row>
     <row r="27">
@@ -2185,22 +3547,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>552186</v>
+        <v>957401</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>52663295.52</v>
+        <v>85160954.81</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>95.37</v>
+        <v>88.95</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>4388607.96</v>
+        <v>3870952.49</v>
       </c>
     </row>
     <row r="28">
@@ -2210,22 +3572,22 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>170</v>
+        <v>487</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>172</v>
+        <v>488</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>102608</v>
+        <v>256110</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>3616256.77</v>
+        <v>9225596.640000001</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>35.24</v>
+        <v>36.02</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>21024.75</v>
+        <v>18904.91</v>
       </c>
     </row>
     <row r="29">
@@ -2235,22 +3597,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>145</v>
+        <v>530</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>226</v>
+        <v>553</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>281044</v>
+        <v>959750</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>18336093.84</v>
+        <v>63617314.07</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>65.23999999999999</v>
+        <v>66.29000000000001</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>81133.16</v>
+        <v>115040.35</v>
       </c>
     </row>
     <row r="30">
@@ -2260,22 +3622,22 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>225072</v>
+        <v>82214</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>50102430</v>
+        <v>11549349.09</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>222.61</v>
+        <v>140.48</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>16700810</v>
+        <v>2309869.82</v>
       </c>
     </row>
     <row r="31">
@@ -2285,28 +3647,28 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>590</v>
+        <v>1756</v>
       </c>
       <c r="C31" s="6" t="n">
-        <v>713</v>
+        <v>1861</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>4536971</v>
+        <v>10717658</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>339837670.33</v>
+        <v>716091241.91</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>74.90000000000001</v>
+        <v>66.81</v>
       </c>
       <c r="G31" s="8" t="n">
-        <v>476630.67</v>
+        <v>384788.42</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>Latest reported show date in this cell: 09/26/2026</t>
+          <t>Latest reported show date in this cell: 09/30/2024</t>
         </is>
       </c>
     </row>
@@ -2541,7 +3903,7 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>Q4 2025 - Live Nation owned/operated</t>
+          <t>Q1 2025 - Live Nation owned/operated</t>
         </is>
       </c>
     </row>
@@ -2589,22 +3951,22 @@
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>261</v>
+        <v>167</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>333</v>
+        <v>208</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>2896875</v>
+        <v>1906635</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>220382837.39</v>
+        <v>132929688.02</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>76.08</v>
+        <v>69.72</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>661810.3199999999</v>
+        <v>639085.04</v>
       </c>
     </row>
     <row r="48">
@@ -2614,22 +3976,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>617458</v>
+        <v>8685</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>43602577.64</v>
+        <v>383060.5</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>70.62</v>
+        <v>44.11</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>703267.38</v>
+        <v>191530.25</v>
       </c>
     </row>
     <row r="49">
@@ -2639,22 +4001,22 @@
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>1883351</v>
+        <v>1201296</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>200947905.15</v>
+        <v>105672603.73</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>106.7</v>
+        <v>87.97</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>6698263.5</v>
+        <v>5870700.21</v>
       </c>
     </row>
     <row r="50">
@@ -2664,22 +4026,22 @@
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>540</v>
+        <v>507</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>547</v>
+        <v>515</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>291662</v>
+        <v>275914</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>9731593.48</v>
+        <v>8767129.42</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>33.37</v>
+        <v>31.77</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>17790.85</v>
+        <v>17023.55</v>
       </c>
     </row>
     <row r="51">
@@ -2689,22 +4051,22 @@
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>691</v>
+        <v>508</v>
       </c>
       <c r="C51" s="3" t="n">
-        <v>862</v>
+        <v>667</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>1223154</v>
+        <v>1017797</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>73986863.09999999</v>
+        <v>56666532.08</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>60.49</v>
+        <v>55.68</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>85831.63</v>
+        <v>84957.32000000001</v>
       </c>
     </row>
     <row r="52">
@@ -2739,28 +4101,1390 @@
         </is>
       </c>
       <c r="B53" s="6" t="n">
-        <v>1573</v>
+        <v>1193</v>
       </c>
       <c r="C53" s="6" t="n">
-        <v>1834</v>
+        <v>1410</v>
       </c>
       <c r="D53" s="6" t="n">
-        <v>6912500</v>
+        <v>4410327</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>548651776.76</v>
+        <v>304419013.75</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>79.37</v>
+        <v>69.02</v>
       </c>
       <c r="G53" s="8" t="n">
-        <v>299155.82</v>
+        <v>215900.01</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="9" t="inlineStr">
         <is>
+          <t>Latest reported show date in this cell: 03/31/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="55"/>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>Q2 2025 - Live Nation owned/operated</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Venue Type</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Num Shows</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Tickets Sold</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Total Gross</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Avg Ticket Price</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>Avg Gross per Show</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>Arena</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>214</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>272</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>2235145</v>
+      </c>
+      <c r="E58" s="4" t="n">
+        <v>172479044.73</v>
+      </c>
+      <c r="F58" s="5" t="n">
+        <v>77.17</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>634114.14</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>Amphitheatre</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>186</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>190</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>2100994</v>
+      </c>
+      <c r="E59" s="4" t="n">
+        <v>127345902.83</v>
+      </c>
+      <c r="F59" s="5" t="n">
+        <v>60.61</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>670241.59</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>Stadium</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>903443</v>
+      </c>
+      <c r="E60" s="4" t="n">
+        <v>94059368.5</v>
+      </c>
+      <c r="F60" s="5" t="n">
+        <v>104.11</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>4702968.43</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>Club</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>567</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>575</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>298903</v>
+      </c>
+      <c r="E61" s="4" t="n">
+        <v>10547885.23</v>
+      </c>
+      <c r="F61" s="5" t="n">
+        <v>35.29</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>18344.15</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>Theater</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>615</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>808</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>1225401</v>
+      </c>
+      <c r="E62" s="4" t="n">
+        <v>72538912.81999999</v>
+      </c>
+      <c r="F62" s="5" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>89775.88</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>27016</v>
+      </c>
+      <c r="E63" s="4" t="n">
+        <v>1203155.48</v>
+      </c>
+      <c r="F63" s="5" t="n">
+        <v>44.53</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>401051.83</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="n">
+        <v>1599</v>
+      </c>
+      <c r="C64" s="6" t="n">
+        <v>1868</v>
+      </c>
+      <c r="D64" s="6" t="n">
+        <v>6790902</v>
+      </c>
+      <c r="E64" s="7" t="n">
+        <v>478174269.59</v>
+      </c>
+      <c r="F64" s="8" t="n">
+        <v>70.41</v>
+      </c>
+      <c r="G64" s="8" t="n">
+        <v>255981.94</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="9" t="inlineStr">
+        <is>
+          <t>Latest reported show date in this cell: 06/30/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="66"/>
+    <row r="67">
+      <c r="A67" s="1" t="inlineStr">
+        <is>
+          <t>Q3 2025 - Live Nation owned/operated</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Venue Type</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Num Shows</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Tickets Sold</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Total Gross</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>Avg Ticket Price</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>Avg Gross per Show</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>Arena</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v>156</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>220</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>2044615</v>
+      </c>
+      <c r="E69" s="4" t="n">
+        <v>157627498.13</v>
+      </c>
+      <c r="F69" s="5" t="n">
+        <v>77.09</v>
+      </c>
+      <c r="G69" s="5" t="n">
+        <v>716488.63</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>Amphitheatre</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v>445</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>460</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>5006953</v>
+      </c>
+      <c r="E70" s="4" t="n">
+        <v>314019966.93</v>
+      </c>
+      <c r="F70" s="5" t="n">
+        <v>62.72</v>
+      </c>
+      <c r="G70" s="5" t="n">
+        <v>682652.1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>Stadium</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>1568735</v>
+      </c>
+      <c r="E71" s="4" t="n">
+        <v>171957973.06</v>
+      </c>
+      <c r="F71" s="5" t="n">
+        <v>109.62</v>
+      </c>
+      <c r="G71" s="5" t="n">
+        <v>5210847.67</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>Club</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v>365</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>365</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>169690</v>
+      </c>
+      <c r="E72" s="4" t="n">
+        <v>5736955.65</v>
+      </c>
+      <c r="F72" s="5" t="n">
+        <v>33.81</v>
+      </c>
+      <c r="G72" s="5" t="n">
+        <v>15717.69</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>Theater</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="n">
+        <v>374</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>496</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>786853</v>
+      </c>
+      <c r="E73" s="4" t="n">
+        <v>54531099.07</v>
+      </c>
+      <c r="F73" s="5" t="n">
+        <v>69.3</v>
+      </c>
+      <c r="G73" s="5" t="n">
+        <v>109941.73</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>453045</v>
+      </c>
+      <c r="E74" s="4" t="n">
+        <v>91726296.7</v>
+      </c>
+      <c r="F74" s="5" t="n">
+        <v>202.47</v>
+      </c>
+      <c r="G74" s="5" t="n">
+        <v>11465787.09</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="n">
+        <v>1365</v>
+      </c>
+      <c r="C75" s="6" t="n">
+        <v>1582</v>
+      </c>
+      <c r="D75" s="6" t="n">
+        <v>10029891</v>
+      </c>
+      <c r="E75" s="7" t="n">
+        <v>795599789.54</v>
+      </c>
+      <c r="F75" s="8" t="n">
+        <v>79.31999999999999</v>
+      </c>
+      <c r="G75" s="8" t="n">
+        <v>502907.58</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="9" t="inlineStr">
+        <is>
+          <t>Latest reported show date in this cell: 09/30/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="77"/>
+    <row r="78">
+      <c r="A78" s="1" t="inlineStr">
+        <is>
+          <t>Q4 2025 - Live Nation owned/operated</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Venue Type</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Num Shows</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Tickets Sold</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>Total Gross</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>Avg Ticket Price</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>Avg Gross per Show</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>Arena</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="n">
+        <v>261</v>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>333</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>2896875</v>
+      </c>
+      <c r="E80" s="4" t="n">
+        <v>220382837.39</v>
+      </c>
+      <c r="F80" s="5" t="n">
+        <v>76.08</v>
+      </c>
+      <c r="G80" s="5" t="n">
+        <v>661810.3199999999</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>Amphitheatre</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>617458</v>
+      </c>
+      <c r="E81" s="4" t="n">
+        <v>43602577.64</v>
+      </c>
+      <c r="F81" s="5" t="n">
+        <v>70.62</v>
+      </c>
+      <c r="G81" s="5" t="n">
+        <v>703267.38</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>Stadium</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>1883351</v>
+      </c>
+      <c r="E82" s="4" t="n">
+        <v>200947905.15</v>
+      </c>
+      <c r="F82" s="5" t="n">
+        <v>106.7</v>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>6698263.5</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>Club</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="n">
+        <v>540</v>
+      </c>
+      <c r="C83" s="3" t="n">
+        <v>547</v>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>291662</v>
+      </c>
+      <c r="E83" s="4" t="n">
+        <v>9731593.48</v>
+      </c>
+      <c r="F83" s="5" t="n">
+        <v>33.37</v>
+      </c>
+      <c r="G83" s="5" t="n">
+        <v>17790.85</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>Theater</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="n">
+        <v>691</v>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>862</v>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>1223154</v>
+      </c>
+      <c r="E84" s="4" t="n">
+        <v>73986863.09999999</v>
+      </c>
+      <c r="F84" s="5" t="n">
+        <v>60.49</v>
+      </c>
+      <c r="G84" s="5" t="n">
+        <v>85831.63</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="n">
+        <v>1573</v>
+      </c>
+      <c r="C86" s="6" t="n">
+        <v>1834</v>
+      </c>
+      <c r="D86" s="6" t="n">
+        <v>6912500</v>
+      </c>
+      <c r="E86" s="7" t="n">
+        <v>548651776.76</v>
+      </c>
+      <c r="F86" s="8" t="n">
+        <v>79.37</v>
+      </c>
+      <c r="G86" s="8" t="n">
+        <v>299155.82</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="9" t="inlineStr">
+        <is>
           <t>Latest reported show date in this cell: 12/31/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="88"/>
+    <row r="89">
+      <c r="A89" s="1" t="inlineStr">
+        <is>
+          <t>Q1 2026 - Live Nation owned/operated</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Venue Type</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Num Shows</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Tickets Sold</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>Total Gross</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>Avg Ticket Price</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>Avg Gross per Show</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>Arena</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="n">
+        <v>163</v>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>191</v>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>1597862</v>
+      </c>
+      <c r="E91" s="4" t="n">
+        <v>133051038.17</v>
+      </c>
+      <c r="F91" s="5" t="n">
+        <v>83.27</v>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>696602.29</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>Amphitheatre</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="C92" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="D92" s="3" t="n">
+        <v>97480</v>
+      </c>
+      <c r="E92" s="4" t="n">
+        <v>7741393.07</v>
+      </c>
+      <c r="F92" s="5" t="n">
+        <v>79.42</v>
+      </c>
+      <c r="G92" s="5" t="n">
+        <v>645116.09</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>Stadium</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="C93" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="D93" s="3" t="n">
+        <v>966039</v>
+      </c>
+      <c r="E93" s="4" t="n">
+        <v>92779544.90000001</v>
+      </c>
+      <c r="F93" s="5" t="n">
+        <v>96.04000000000001</v>
+      </c>
+      <c r="G93" s="5" t="n">
+        <v>6185302.99</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>Club</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="n">
+        <v>470</v>
+      </c>
+      <c r="C94" s="3" t="n">
+        <v>479</v>
+      </c>
+      <c r="D94" s="3" t="n">
+        <v>285073</v>
+      </c>
+      <c r="E94" s="4" t="n">
+        <v>9705020.98</v>
+      </c>
+      <c r="F94" s="5" t="n">
+        <v>34.04</v>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>20261</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>Theater</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="n">
+        <v>406</v>
+      </c>
+      <c r="C95" s="3" t="n">
+        <v>587</v>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>851422</v>
+      </c>
+      <c r="E95" s="4" t="n">
+        <v>53737151.35</v>
+      </c>
+      <c r="F95" s="5" t="n">
+        <v>63.11</v>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>91545.39999999999</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B97" s="6" t="n">
+        <v>1061</v>
+      </c>
+      <c r="C97" s="6" t="n">
+        <v>1284</v>
+      </c>
+      <c r="D97" s="6" t="n">
+        <v>3797876</v>
+      </c>
+      <c r="E97" s="7" t="n">
+        <v>297014148.47</v>
+      </c>
+      <c r="F97" s="8" t="n">
+        <v>78.20999999999999</v>
+      </c>
+      <c r="G97" s="8" t="n">
+        <v>231319.43</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="9" t="inlineStr">
+        <is>
+          <t>Latest reported show date in this cell: 03/31/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="99"/>
+    <row r="100">
+      <c r="A100" s="1" t="inlineStr">
+        <is>
+          <t>Q2 2026 - Live Nation owned/operated</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>Venue Type</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Num Shows</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Tickets Sold</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>Total Gross</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>Avg Ticket Price</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>Avg Gross per Show</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>Arena</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="n">
+        <v>219</v>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>245</v>
+      </c>
+      <c r="D102" s="3" t="n">
+        <v>2301168</v>
+      </c>
+      <c r="E102" s="4" t="n">
+        <v>225036474.52</v>
+      </c>
+      <c r="F102" s="5" t="n">
+        <v>97.79000000000001</v>
+      </c>
+      <c r="G102" s="5" t="n">
+        <v>918516.22</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>Amphitheatre</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="n">
+        <v>151</v>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>158</v>
+      </c>
+      <c r="D103" s="3" t="n">
+        <v>1942906</v>
+      </c>
+      <c r="E103" s="4" t="n">
+        <v>149753592.26</v>
+      </c>
+      <c r="F103" s="5" t="n">
+        <v>77.08</v>
+      </c>
+      <c r="G103" s="5" t="n">
+        <v>947807.55</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>Stadium</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="C104" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D104" s="3" t="n">
+        <v>1083339</v>
+      </c>
+      <c r="E104" s="4" t="n">
+        <v>139149410.61</v>
+      </c>
+      <c r="F104" s="5" t="n">
+        <v>128.44</v>
+      </c>
+      <c r="G104" s="5" t="n">
+        <v>5797892.11</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>Club</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="n">
+        <v>495</v>
+      </c>
+      <c r="C105" s="3" t="n">
+        <v>499</v>
+      </c>
+      <c r="D105" s="3" t="n">
+        <v>284360</v>
+      </c>
+      <c r="E105" s="4" t="n">
+        <v>10029164.59</v>
+      </c>
+      <c r="F105" s="5" t="n">
+        <v>35.27</v>
+      </c>
+      <c r="G105" s="5" t="n">
+        <v>20098.53</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>Theater</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="n">
+        <v>442</v>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>613</v>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>772568</v>
+      </c>
+      <c r="E106" s="4" t="n">
+        <v>45801895.14</v>
+      </c>
+      <c r="F106" s="5" t="n">
+        <v>59.29</v>
+      </c>
+      <c r="G106" s="5" t="n">
+        <v>74717.61</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B108" s="6" t="n">
+        <v>1327</v>
+      </c>
+      <c r="C108" s="6" t="n">
+        <v>1539</v>
+      </c>
+      <c r="D108" s="6" t="n">
+        <v>6384341</v>
+      </c>
+      <c r="E108" s="7" t="n">
+        <v>569770537.12</v>
+      </c>
+      <c r="F108" s="8" t="n">
+        <v>89.25</v>
+      </c>
+      <c r="G108" s="8" t="n">
+        <v>370221.27</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="9" t="inlineStr">
+        <is>
+          <t>Latest reported show date in this cell: 06/30/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="110"/>
+    <row r="111">
+      <c r="A111" s="1" t="inlineStr">
+        <is>
+          <t>Q3 2026 - Live Nation owned/operated</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>Venue Type</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Num Shows</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Tickets Sold</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>Total Gross</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>Avg Ticket Price</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>Avg Gross per Show</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>Arena</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="C113" s="3" t="n">
+        <v>102</v>
+      </c>
+      <c r="D113" s="3" t="n">
+        <v>844983</v>
+      </c>
+      <c r="E113" s="4" t="n">
+        <v>61674894.82</v>
+      </c>
+      <c r="F113" s="5" t="n">
+        <v>72.98999999999999</v>
+      </c>
+      <c r="G113" s="5" t="n">
+        <v>604655.83</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="inlineStr">
+        <is>
+          <t>Amphitheatre</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="n">
+        <v>193</v>
+      </c>
+      <c r="C114" s="3" t="n">
+        <v>198</v>
+      </c>
+      <c r="D114" s="3" t="n">
+        <v>2531078</v>
+      </c>
+      <c r="E114" s="4" t="n">
+        <v>153444699.38</v>
+      </c>
+      <c r="F114" s="5" t="n">
+        <v>60.62</v>
+      </c>
+      <c r="G114" s="5" t="n">
+        <v>774973.23</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>Stadium</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="D115" s="3" t="n">
+        <v>552186</v>
+      </c>
+      <c r="E115" s="4" t="n">
+        <v>52663295.52</v>
+      </c>
+      <c r="F115" s="5" t="n">
+        <v>95.37</v>
+      </c>
+      <c r="G115" s="5" t="n">
+        <v>4388607.96</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="inlineStr">
+        <is>
+          <t>Club</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="n">
+        <v>170</v>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>172</v>
+      </c>
+      <c r="D116" s="3" t="n">
+        <v>102608</v>
+      </c>
+      <c r="E116" s="4" t="n">
+        <v>3616256.77</v>
+      </c>
+      <c r="F116" s="5" t="n">
+        <v>35.24</v>
+      </c>
+      <c r="G116" s="5" t="n">
+        <v>21024.75</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>Theater</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="n">
+        <v>145</v>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>226</v>
+      </c>
+      <c r="D117" s="3" t="n">
+        <v>281044</v>
+      </c>
+      <c r="E117" s="4" t="n">
+        <v>18336093.84</v>
+      </c>
+      <c r="F117" s="5" t="n">
+        <v>65.23999999999999</v>
+      </c>
+      <c r="G117" s="5" t="n">
+        <v>81133.16</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D118" s="3" t="n">
+        <v>225072</v>
+      </c>
+      <c r="E118" s="4" t="n">
+        <v>50102430</v>
+      </c>
+      <c r="F118" s="5" t="n">
+        <v>222.61</v>
+      </c>
+      <c r="G118" s="5" t="n">
+        <v>16700810</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="6" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B119" s="6" t="n">
+        <v>590</v>
+      </c>
+      <c r="C119" s="6" t="n">
+        <v>713</v>
+      </c>
+      <c r="D119" s="6" t="n">
+        <v>4536971</v>
+      </c>
+      <c r="E119" s="7" t="n">
+        <v>339837670.33</v>
+      </c>
+      <c r="F119" s="8" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="G119" s="8" t="n">
+        <v>476630.67</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="9" t="inlineStr">
+        <is>
+          <t>Latest reported show date in this cell: 09/26/2026</t>
         </is>
       </c>
     </row>
@@ -2775,10 +5499,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="1" max="1"/>
     <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -2814,79 +5538,331 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Q3 = Jul 1 - Sep 30, Q4 = Oct 1 - Dec 31. Cells reported: Q3 2024, Q3 2025, Q3 2026, Q4 2024, Q4 2025. Q4 2026 is excluded (does not exist yet).</t>
+          <t>Cells reported: Q1 2024, Q2 2024, Q3 2024, Q4 2024, Q1 2025, Q2 2025, Q3 2025, Q4 2025, Q1 2026, Q2 2026, Q3 2026. Q3 = Jul 1 - Sep 30, Q4 = Oct 1 - Dec 31.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="12" t="inlineStr">
         <is>
-          <t>Latest reported date, Q3 2026 - promoted</t>
+          <t>Current-year coverage</t>
         </is>
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>09/27/2026</t>
+          <t>2026 is reported through Q3 only; Q4 2026 has not happened yet and is excluded.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
         <is>
-          <t>Latest reported date, Q3 2026 - owned/operated</t>
+          <t>Reporting lag</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>09/26/2026</t>
+          <t>Pollstar is pulled with a lag, so the latest cell (Q3 2026) is incomplete by construction: recent show dates have not landed yet. The latest reported date below the cell is its effective right edge. All earlier cells are settled and complete.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>Reporting lag</t>
+          <t>Promoted basis</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Pollstar is pulled with a lag, so Q3 2026 is incomplete by construction: recent show dates have not landed yet. The latest reported date above is the effective right edge of the current-year Q3 window. Q3 2024 and Q3 2025 are settled.</t>
+          <t>promoter matches (case-insensitive): live nation, ocesa, c3, cuffe &amp; taylor, df concerts, emporium presents, festival republic, frank productions, house of blues, mcd productions. Venue type from the row's companyType (analyze_venues.py parity).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>Promoted basis</t>
+          <t>Owned/operated basis</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>promoter matches (case-insensitive): live nation, ocesa, c3, cuffe &amp; taylor, df concerts, emporium presents, festival republic, frank productions, house of blues, mcd productions. Venue type from the row's companyType (analyze_venues.py parity).</t>
+          <t>venueName + city matched to venuenames.xlsx via pipeline_config (exact city, token_set_ratio &gt;= 85, all rows used, relationship not a filter). Venue type from the matched reference venue.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>Owned/operated basis</t>
+          <t>Units</t>
         </is>
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>venueName + city matched to venuenames.xlsx via pipeline_config (exact city, token_set_ratio &gt;= 85, all rows used, relationship not a filter). Venue type from the matched reference venue.</t>
+          <t>ticketsSold and grossUSD are per-engagement totals and are summed as-is, never multiplied by numShows. Count = engagement rows. Avg Ticket Price = Total Gross / Tickets Sold. Avg Gross per Show = Total Gross / Num Shows (matches analyze_venues.py venue pivot).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>Units</t>
+          <t>Latest reported date, Q1 2024 - promoted</t>
         </is>
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>ticketsSold and grossUSD are per-engagement totals and are summed as-is, never multiplied by numShows. Count = engagement rows. Avg Ticket Price = Total Gross / Tickets Sold. Avg Gross per Show = Total Gross / Num Shows (matches analyze_venues.py venue pivot).</t>
+          <t>03/31/2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>Latest reported date, Q1 2024 - owned/operated</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>03/31/2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>Latest reported date, Q2 2024 - promoted</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>06/30/2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>Latest reported date, Q2 2024 - owned/operated</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>06/30/2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>Latest reported date, Q3 2024 - promoted</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>09/30/2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>Latest reported date, Q3 2024 - owned/operated</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>09/30/2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Latest reported date, Q4 2024 - promoted</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>12/31/2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>Latest reported date, Q4 2024 - owned/operated</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>12/31/2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>Latest reported date, Q1 2025 - promoted</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>03/31/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>Latest reported date, Q1 2025 - owned/operated</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>03/31/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>Latest reported date, Q2 2025 - promoted</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>06/30/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>Latest reported date, Q2 2025 - owned/operated</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>06/30/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>Latest reported date, Q3 2025 - promoted</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>09/30/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>Latest reported date, Q3 2025 - owned/operated</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>09/30/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>Latest reported date, Q4 2025 - promoted</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>12/31/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>Latest reported date, Q4 2025 - owned/operated</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>12/31/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>Latest reported date, Q1 2026 - promoted</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>03/31/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>Latest reported date, Q1 2026 - owned/operated</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>03/31/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>Latest reported date, Q2 2026 - promoted</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>06/30/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>Latest reported date, Q2 2026 - owned/operated</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>06/30/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>Latest reported date, Q3 2026 - promoted</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>09/27/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>Latest reported date, Q3 2026 - owned/operated</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>09/26/2026</t>
         </is>
       </c>
     </row>

--- a/Q3_Q4_LYV_venue_pivots.xlsx
+++ b/Q3_Q4_LYV_venue_pivots.xlsx
@@ -9,7 +9,8 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LN Promoted" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LN Owned-Operated" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pivot" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +23,7 @@
     <numFmt numFmtId="164" formatCode="$#,##0"/>
     <numFmt numFmtId="165" formatCode="$#,##0.00"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,6 +42,7 @@
       <i val="1"/>
       <sz val="9"/>
     </font>
+    <font/>
   </fonts>
   <fills count="3">
     <fill>
@@ -73,7 +75,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -84,6 +86,14 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
@@ -5499,7 +5509,1539 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:M39"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Reported Gross by venue type - Live Nation promoted</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>Venue Type</t>
+        </is>
+      </c>
+      <c r="B2" s="11" t="inlineStr">
+        <is>
+          <t>1Q24</t>
+        </is>
+      </c>
+      <c r="C2" s="11" t="inlineStr">
+        <is>
+          <t>2Q24</t>
+        </is>
+      </c>
+      <c r="D2" s="11" t="inlineStr">
+        <is>
+          <t>3Q24</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>4Q24</t>
+        </is>
+      </c>
+      <c r="F2" s="11" t="inlineStr">
+        <is>
+          <t>1Q25</t>
+        </is>
+      </c>
+      <c r="G2" s="11" t="inlineStr">
+        <is>
+          <t>2Q25</t>
+        </is>
+      </c>
+      <c r="H2" s="11" t="inlineStr">
+        <is>
+          <t>3Q25</t>
+        </is>
+      </c>
+      <c r="I2" s="11" t="inlineStr">
+        <is>
+          <t>4Q25</t>
+        </is>
+      </c>
+      <c r="J2" s="11" t="inlineStr">
+        <is>
+          <t>1Q26</t>
+        </is>
+      </c>
+      <c r="K2" s="11" t="inlineStr">
+        <is>
+          <t>2Q26</t>
+        </is>
+      </c>
+      <c r="L2" s="11" t="inlineStr">
+        <is>
+          <t>3Q26</t>
+        </is>
+      </c>
+      <c r="M2" s="11" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>Arena</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="n">
+        <v>885217552.1799999</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>1141372999.72</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>1020346599.55</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>1047858852.85</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>538814765.8200001</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>653364259.74</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>959468671.88</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>905548614.2</v>
+      </c>
+      <c r="J3" s="4" t="n">
+        <v>580938201.4400001</v>
+      </c>
+      <c r="K3" s="4" t="n">
+        <v>827929963.45</v>
+      </c>
+      <c r="L3" s="4" t="n">
+        <v>580123925.65</v>
+      </c>
+      <c r="M3" s="4" t="n">
+        <v>9140984406.48</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Amphitheatre</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>10928098.05</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>253854462.29</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>521398460.91</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>84565704.68000001</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>4870489.91</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>170544780.04</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>392129657.64</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>70825655.51000001</v>
+      </c>
+      <c r="J4" s="4" t="n">
+        <v>8681755.67</v>
+      </c>
+      <c r="K4" s="4" t="n">
+        <v>167776894.49</v>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>212107689.02</v>
+      </c>
+      <c r="M4" s="4" t="n">
+        <v>1897683648.21</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>Stadium</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>404396755.15</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>314604148.68</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>1038171101.51</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>587801659.52</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>326785015.49</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>1818858263.01</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>1463972588.76</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>579357268.86</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>426460735.85</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>763312703.41</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>1510081963.63</v>
+      </c>
+      <c r="M5" s="4" t="n">
+        <v>9233802203.870001</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Club</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>17854773.91</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>28129039.6</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>33634694.65</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>31416065.55</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>20038961.68</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>30345218.1</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>24300468.53</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>27987293.1</v>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>18373295.76</v>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>27094459.44</v>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>16236818.33</v>
+      </c>
+      <c r="M6" s="4" t="n">
+        <v>275411088.65</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Theater</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>125598660.55</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>180892765.66</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>156322089.93</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>163138067.71</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>119478048.05</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>143858849.19</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>115519649.75</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>183400099.65</v>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>131486826.62</v>
+      </c>
+      <c r="K7" s="4" t="n">
+        <v>137692516.23</v>
+      </c>
+      <c r="L7" s="4" t="n">
+        <v>60574122.36</v>
+      </c>
+      <c r="M7" s="4" t="n">
+        <v>1517961695.7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>20897937.73</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>36465906.47</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>63120340.25</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>8444488.68</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>18024875.82</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>37029275.76</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>67496108.45</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>28775898.24</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>15752274.9</v>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>32497605.14</v>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>38199002.05</v>
+      </c>
+      <c r="M8" s="4" t="n">
+        <v>366703713.49</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n">
+        <v>1464893777.57</v>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>1955319322.42</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>2832993286.8</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>1923224838.99</v>
+      </c>
+      <c r="F9" s="7" t="n">
+        <v>1028012156.77</v>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>2854000645.84</v>
+      </c>
+      <c r="H9" s="7" t="n">
+        <v>3022887145.01</v>
+      </c>
+      <c r="I9" s="7" t="n">
+        <v>1795894829.56</v>
+      </c>
+      <c r="J9" s="7" t="n">
+        <v>1181693090.24</v>
+      </c>
+      <c r="K9" s="7" t="n">
+        <v>1956304142.16</v>
+      </c>
+      <c r="L9" s="7" t="n">
+        <v>2417323521.04</v>
+      </c>
+      <c r="M9" s="7" t="n">
+        <v>22432546756.4</v>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Show Count by venue type - Live Nation promoted</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>Venue Type</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>1Q24</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>2Q24</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>3Q24</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>4Q24</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="inlineStr">
+        <is>
+          <t>1Q25</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>2Q25</t>
+        </is>
+      </c>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>3Q25</t>
+        </is>
+      </c>
+      <c r="I12" s="11" t="inlineStr">
+        <is>
+          <t>4Q25</t>
+        </is>
+      </c>
+      <c r="J12" s="11" t="inlineStr">
+        <is>
+          <t>1Q26</t>
+        </is>
+      </c>
+      <c r="K12" s="11" t="inlineStr">
+        <is>
+          <t>2Q26</t>
+        </is>
+      </c>
+      <c r="L12" s="11" t="inlineStr">
+        <is>
+          <t>3Q26</t>
+        </is>
+      </c>
+      <c r="M12" s="11" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>Arena</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>625</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>897</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>831</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>986</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>446</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>650</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>726</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>897</v>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>470</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>677</v>
+      </c>
+      <c r="L13" s="3" t="n">
+        <v>381</v>
+      </c>
+      <c r="M13" s="3" t="n">
+        <v>7586</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>Amphitheatre</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>328</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>733</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>107</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>265</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>583</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>106</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>209</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>265</v>
+      </c>
+      <c r="M14" s="3" t="n">
+        <v>2649</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Stadium</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>77</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>108</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>205</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>138</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>356</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>285</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="J15" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>163</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>202</v>
+      </c>
+      <c r="M15" s="3" t="n">
+        <v>1801</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>Club</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>574</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>749</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>635</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>808</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>619</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>771</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>519</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>837</v>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>563</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>1313</v>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>206</v>
+      </c>
+      <c r="M16" s="3" t="n">
+        <v>7594</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>Theater</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>806</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>965</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>824</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>1119</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>697</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>810</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>623</v>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>1150</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>890</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>956</v>
+      </c>
+      <c r="L17" s="3" t="n">
+        <v>379</v>
+      </c>
+      <c r="M17" s="3" t="n">
+        <v>9219</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>126</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>153</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>157</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>86</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="L18" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="M18" s="3" t="n">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>2162</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>3173</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>3381</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>3315</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>1931</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>2925</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>2822</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>3208</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>2050</v>
+      </c>
+      <c r="K19" s="6" t="n">
+        <v>3400</v>
+      </c>
+      <c r="L19" s="6" t="n">
+        <v>1449</v>
+      </c>
+      <c r="M19" s="6" t="n">
+        <v>29816</v>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>Reported Gross by venue type - Live Nation owned/operated</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>Venue Type</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>1Q24</t>
+        </is>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>2Q24</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>3Q24</t>
+        </is>
+      </c>
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>4Q24</t>
+        </is>
+      </c>
+      <c r="F22" s="11" t="inlineStr">
+        <is>
+          <t>1Q25</t>
+        </is>
+      </c>
+      <c r="G22" s="11" t="inlineStr">
+        <is>
+          <t>2Q25</t>
+        </is>
+      </c>
+      <c r="H22" s="11" t="inlineStr">
+        <is>
+          <t>3Q25</t>
+        </is>
+      </c>
+      <c r="I22" s="11" t="inlineStr">
+        <is>
+          <t>4Q25</t>
+        </is>
+      </c>
+      <c r="J22" s="11" t="inlineStr">
+        <is>
+          <t>1Q26</t>
+        </is>
+      </c>
+      <c r="K22" s="11" t="inlineStr">
+        <is>
+          <t>2Q26</t>
+        </is>
+      </c>
+      <c r="L22" s="11" t="inlineStr">
+        <is>
+          <t>3Q26</t>
+        </is>
+      </c>
+      <c r="M22" s="11" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>Arena</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>91194066.40000001</v>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>186977791.47</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>108583236.38</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>155293667.95</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>132929688.02</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>172479044.73</v>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>157627498.13</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>220382837.39</v>
+      </c>
+      <c r="J23" s="4" t="n">
+        <v>133051038.17</v>
+      </c>
+      <c r="K23" s="4" t="n">
+        <v>225036474.52</v>
+      </c>
+      <c r="L23" s="4" t="n">
+        <v>61674894.82</v>
+      </c>
+      <c r="M23" s="4" t="n">
+        <v>1645230237.98</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>Amphitheatre</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>1595404.5</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>189117373.17</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>437954790.92</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>55377701.95</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>383060.5</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>127345902.83</v>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>314019966.93</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>43602577.64</v>
+      </c>
+      <c r="J24" s="4" t="n">
+        <v>7741393.07</v>
+      </c>
+      <c r="K24" s="4" t="n">
+        <v>149753592.26</v>
+      </c>
+      <c r="L24" s="4" t="n">
+        <v>153444699.38</v>
+      </c>
+      <c r="M24" s="4" t="n">
+        <v>1480336463.15</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>Stadium</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>36070342.33</v>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>22404216.67</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>85160954.81</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>147785050.97</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>105672603.73</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>94059368.5</v>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>171957973.06</v>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>200947905.15</v>
+      </c>
+      <c r="J25" s="4" t="n">
+        <v>92779544.90000001</v>
+      </c>
+      <c r="K25" s="4" t="n">
+        <v>139149410.61</v>
+      </c>
+      <c r="L25" s="4" t="n">
+        <v>52663295.52</v>
+      </c>
+      <c r="M25" s="4" t="n">
+        <v>1148650666.25</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>Club</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>8760935.92</v>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>10844626.51</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>9225596.640000001</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>12358843.72</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>8767129.42</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>10547885.23</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>5736955.65</v>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>9731593.48</v>
+      </c>
+      <c r="J26" s="4" t="n">
+        <v>9705020.98</v>
+      </c>
+      <c r="K26" s="4" t="n">
+        <v>10029164.59</v>
+      </c>
+      <c r="L26" s="4" t="n">
+        <v>3616256.77</v>
+      </c>
+      <c r="M26" s="4" t="n">
+        <v>99324008.91</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>Theater</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>52753830.57</v>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>64430933.18</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>63617314.07</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>87028089.70999999</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>56666532.08</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>72538912.81999999</v>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>54531099.07</v>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>73986863.09999999</v>
+      </c>
+      <c r="J27" s="4" t="n">
+        <v>53737151.35</v>
+      </c>
+      <c r="K27" s="4" t="n">
+        <v>45801895.14</v>
+      </c>
+      <c r="L27" s="4" t="n">
+        <v>18336093.84</v>
+      </c>
+      <c r="M27" s="4" t="n">
+        <v>643428714.9299999</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>853662.2</v>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>11549349.09</v>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>1203155.48</v>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>91726296.7</v>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="4" t="n">
+        <v>50102430</v>
+      </c>
+      <c r="M28" s="4" t="n">
+        <v>155434893.47</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="n">
+        <v>190374579.72</v>
+      </c>
+      <c r="C29" s="7" t="n">
+        <v>474628603.2</v>
+      </c>
+      <c r="D29" s="7" t="n">
+        <v>716091241.91</v>
+      </c>
+      <c r="E29" s="7" t="n">
+        <v>457843354.3</v>
+      </c>
+      <c r="F29" s="7" t="n">
+        <v>304419013.75</v>
+      </c>
+      <c r="G29" s="7" t="n">
+        <v>478174269.59</v>
+      </c>
+      <c r="H29" s="7" t="n">
+        <v>795599789.54</v>
+      </c>
+      <c r="I29" s="7" t="n">
+        <v>548651776.76</v>
+      </c>
+      <c r="J29" s="7" t="n">
+        <v>297014148.47</v>
+      </c>
+      <c r="K29" s="7" t="n">
+        <v>569770537.12</v>
+      </c>
+      <c r="L29" s="7" t="n">
+        <v>339837670.33</v>
+      </c>
+      <c r="M29" s="7" t="n">
+        <v>5172404984.69</v>
+      </c>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>Show Count by venue type - Live Nation owned/operated</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>Venue Type</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>1Q24</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>2Q24</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="inlineStr">
+        <is>
+          <t>3Q24</t>
+        </is>
+      </c>
+      <c r="E32" s="11" t="inlineStr">
+        <is>
+          <t>4Q24</t>
+        </is>
+      </c>
+      <c r="F32" s="11" t="inlineStr">
+        <is>
+          <t>1Q25</t>
+        </is>
+      </c>
+      <c r="G32" s="11" t="inlineStr">
+        <is>
+          <t>2Q25</t>
+        </is>
+      </c>
+      <c r="H32" s="11" t="inlineStr">
+        <is>
+          <t>3Q25</t>
+        </is>
+      </c>
+      <c r="I32" s="11" t="inlineStr">
+        <is>
+          <t>4Q25</t>
+        </is>
+      </c>
+      <c r="J32" s="11" t="inlineStr">
+        <is>
+          <t>1Q26</t>
+        </is>
+      </c>
+      <c r="K32" s="11" t="inlineStr">
+        <is>
+          <t>2Q26</t>
+        </is>
+      </c>
+      <c r="L32" s="11" t="inlineStr">
+        <is>
+          <t>3Q26</t>
+        </is>
+      </c>
+      <c r="M32" s="11" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>Arena</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>272</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>196</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>295</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>208</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>272</v>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>220</v>
+      </c>
+      <c r="I33" s="3" t="n">
+        <v>333</v>
+      </c>
+      <c r="J33" s="3" t="n">
+        <v>191</v>
+      </c>
+      <c r="K33" s="3" t="n">
+        <v>245</v>
+      </c>
+      <c r="L33" s="3" t="n">
+        <v>102</v>
+      </c>
+      <c r="M33" s="3" t="n">
+        <v>2509</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>Amphitheatre</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>245</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>597</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>190</v>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>460</v>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="J34" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="K34" s="3" t="n">
+        <v>158</v>
+      </c>
+      <c r="L34" s="3" t="n">
+        <v>198</v>
+      </c>
+      <c r="M34" s="3" t="n">
+        <v>2004</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>Stadium</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="I35" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="J35" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="K35" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="L35" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="M35" s="3" t="n">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>Club</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>501</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>637</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>488</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>642</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>515</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>575</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>365</v>
+      </c>
+      <c r="I36" s="3" t="n">
+        <v>547</v>
+      </c>
+      <c r="J36" s="3" t="n">
+        <v>479</v>
+      </c>
+      <c r="K36" s="3" t="n">
+        <v>499</v>
+      </c>
+      <c r="L36" s="3" t="n">
+        <v>172</v>
+      </c>
+      <c r="M36" s="3" t="n">
+        <v>5420</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>Theater</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>583</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>647</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>553</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>878</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>667</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>808</v>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>496</v>
+      </c>
+      <c r="I37" s="3" t="n">
+        <v>862</v>
+      </c>
+      <c r="J37" s="3" t="n">
+        <v>587</v>
+      </c>
+      <c r="K37" s="3" t="n">
+        <v>613</v>
+      </c>
+      <c r="L37" s="3" t="n">
+        <v>226</v>
+      </c>
+      <c r="M37" s="3" t="n">
+        <v>6920</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H38" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="I38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="M38" s="3" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="13" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="n">
+        <v>1270</v>
+      </c>
+      <c r="C39" s="6" t="n">
+        <v>1810</v>
+      </c>
+      <c r="D39" s="6" t="n">
+        <v>1861</v>
+      </c>
+      <c r="E39" s="6" t="n">
+        <v>1918</v>
+      </c>
+      <c r="F39" s="6" t="n">
+        <v>1410</v>
+      </c>
+      <c r="G39" s="6" t="n">
+        <v>1868</v>
+      </c>
+      <c r="H39" s="6" t="n">
+        <v>1582</v>
+      </c>
+      <c r="I39" s="6" t="n">
+        <v>1834</v>
+      </c>
+      <c r="J39" s="6" t="n">
+        <v>1284</v>
+      </c>
+      <c r="K39" s="6" t="n">
+        <v>1539</v>
+      </c>
+      <c r="L39" s="6" t="n">
+        <v>713</v>
+      </c>
+      <c r="M39" s="6" t="n">
+        <v>17089</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -5507,360 +7049,372 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="17" t="inlineStr">
         <is>
           <t>pollstar/concerts.csv. One row = one engagement.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>Cells reported: Q1 2024, Q2 2024, Q3 2024, Q4 2024, Q1 2025, Q2 2025, Q3 2025, Q4 2025, Q1 2026, Q2 2026, Q3 2026. Q3 = Jul 1 - Sep 30, Q4 = Oct 1 - Dec 31.</t>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>Cells reported: 1Q24, 2Q24, 3Q24, 4Q24, 1Q25, 2Q25, 3Q25, 4Q25, 1Q26, 2Q26, 3Q26. Q3 = Jul 1 - Sep 30, Q4 = Oct 1 - Dec 31.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Current-year coverage</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>2026 is reported through Q3 only; Q4 2026 has not happened yet and is excluded.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Reporting lag</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>Pollstar is pulled with a lag, so the latest cell (Q3 2026) is incomplete by construction: recent show dates have not landed yet. The latest reported date below the cell is its effective right edge. All earlier cells are settled and complete.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Promoted basis</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>promoter matches (case-insensitive): live nation, ocesa, c3, cuffe &amp; taylor, df concerts, emporium presents, festival republic, frank productions, house of blues, mcd productions. Venue type from the row's companyType (analyze_venues.py parity).</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Owned/operated basis</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>venueName + city matched to venuenames.xlsx via pipeline_config (exact city, token_set_ratio &gt;= 85, all rows used, relationship not a filter). Venue type from the matched reference venue.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>Pivot sheet</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>'Reported Gross' = sum of grossUSD. 'Show Count' = sum of numShows (performances), not engagement rows. Both are shown per basis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>ticketsSold and grossUSD are per-engagement totals and are summed as-is, never multiplied by numShows. Count = engagement rows. Avg Ticket Price = Total Gross / Tickets Sold. Avg Gross per Show = Total Gross / Num Shows (matches analyze_venues.py venue pivot).</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>Latest reported date, Q1 2024 - promoted</t>
-        </is>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>Latest reported date, 1Q24 - promoted</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>03/31/2024</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>Latest reported date, Q1 2024 - owned/operated</t>
-        </is>
-      </c>
-      <c r="B10" s="13" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>Latest reported date, 1Q24 - owned/operated</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>03/31/2024</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>Latest reported date, Q2 2024 - promoted</t>
-        </is>
-      </c>
-      <c r="B11" s="13" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>Latest reported date, 2Q24 - promoted</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>06/30/2024</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>Latest reported date, Q2 2024 - owned/operated</t>
-        </is>
-      </c>
-      <c r="B12" s="13" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>Latest reported date, 2Q24 - owned/operated</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>06/30/2024</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>Latest reported date, Q3 2024 - promoted</t>
-        </is>
-      </c>
-      <c r="B13" s="13" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>Latest reported date, 3Q24 - promoted</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>09/30/2024</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>Latest reported date, Q3 2024 - owned/operated</t>
-        </is>
-      </c>
-      <c r="B14" s="13" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>Latest reported date, 3Q24 - owned/operated</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>09/30/2024</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>Latest reported date, Q4 2024 - promoted</t>
-        </is>
-      </c>
-      <c r="B15" s="13" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>Latest reported date, 4Q24 - promoted</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>12/31/2024</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>Latest reported date, Q4 2024 - owned/operated</t>
-        </is>
-      </c>
-      <c r="B16" s="13" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>Latest reported date, 4Q24 - owned/operated</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>12/31/2024</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>Latest reported date, Q1 2025 - promoted</t>
-        </is>
-      </c>
-      <c r="B17" s="13" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>Latest reported date, 1Q25 - promoted</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="inlineStr">
         <is>
           <t>03/31/2025</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>Latest reported date, Q1 2025 - owned/operated</t>
-        </is>
-      </c>
-      <c r="B18" s="13" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>Latest reported date, 1Q25 - owned/operated</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
         <is>
           <t>03/31/2025</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>Latest reported date, Q2 2025 - promoted</t>
-        </is>
-      </c>
-      <c r="B19" s="13" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>Latest reported date, 2Q25 - promoted</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="inlineStr">
         <is>
           <t>06/30/2025</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>Latest reported date, Q2 2025 - owned/operated</t>
-        </is>
-      </c>
-      <c r="B20" s="13" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t>Latest reported date, 2Q25 - owned/operated</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="inlineStr">
         <is>
           <t>06/30/2025</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>Latest reported date, Q3 2025 - promoted</t>
-        </is>
-      </c>
-      <c r="B21" s="13" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>Latest reported date, 3Q25 - promoted</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="inlineStr">
         <is>
           <t>09/30/2025</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>Latest reported date, Q3 2025 - owned/operated</t>
-        </is>
-      </c>
-      <c r="B22" s="13" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>Latest reported date, 3Q25 - owned/operated</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="inlineStr">
         <is>
           <t>09/30/2025</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>Latest reported date, Q4 2025 - promoted</t>
-        </is>
-      </c>
-      <c r="B23" s="13" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="16" t="inlineStr">
+        <is>
+          <t>Latest reported date, 4Q25 - promoted</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="inlineStr">
         <is>
           <t>12/31/2025</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>Latest reported date, Q4 2025 - owned/operated</t>
-        </is>
-      </c>
-      <c r="B24" s="13" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>Latest reported date, 4Q25 - owned/operated</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="inlineStr">
         <is>
           <t>12/31/2025</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>Latest reported date, Q1 2026 - promoted</t>
-        </is>
-      </c>
-      <c r="B25" s="13" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>Latest reported date, 1Q26 - promoted</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="inlineStr">
         <is>
           <t>03/31/2026</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>Latest reported date, Q1 2026 - owned/operated</t>
-        </is>
-      </c>
-      <c r="B26" s="13" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t>Latest reported date, 1Q26 - owned/operated</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="inlineStr">
         <is>
           <t>03/31/2026</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>Latest reported date, Q2 2026 - promoted</t>
-        </is>
-      </c>
-      <c r="B27" s="13" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>Latest reported date, 2Q26 - promoted</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="inlineStr">
         <is>
           <t>06/30/2026</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t>Latest reported date, Q2 2026 - owned/operated</t>
-        </is>
-      </c>
-      <c r="B28" s="13" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>Latest reported date, 2Q26 - owned/operated</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="inlineStr">
         <is>
           <t>06/30/2026</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="12" t="inlineStr">
-        <is>
-          <t>Latest reported date, Q3 2026 - promoted</t>
-        </is>
-      </c>
-      <c r="B29" s="13" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="16" t="inlineStr">
+        <is>
+          <t>Latest reported date, 3Q26 - promoted</t>
+        </is>
+      </c>
+      <c r="B30" s="17" t="inlineStr">
         <is>
           <t>09/27/2026</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="12" t="inlineStr">
-        <is>
-          <t>Latest reported date, Q3 2026 - owned/operated</t>
-        </is>
-      </c>
-      <c r="B30" s="13" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>Latest reported date, 3Q26 - owned/operated</t>
+        </is>
+      </c>
+      <c r="B31" s="17" t="inlineStr">
         <is>
           <t>09/26/2026</t>
         </is>
